--- a/content/tz-dzen-pochemu-kitaj-podnebesnaya.xlsx
+++ b/content/tz-dzen-pochemu-kitaj-podnebesnaya.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -970,22 +970,10 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Финал</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>аккордеон, 4–5 вопросов</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Финал</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>подпись автора (нейтральная), хэштеги, источники</t>
         </is>
@@ -1259,7 +1247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1317,58 +1305,10 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>FAQ 1</t>
+          <t>Подпись-финал</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Что значит «Поднебесная»? — Русский перевод 天下 (tiānxià) — «[всё] под небом», весь мир под властью императора.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>FAQ 2</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Почему именно Китай так называют? — По древней картине мира император-«Сын Неба» правил всей землёй «под небом», а Китай был её центром.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>FAQ 3</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>А 中国 — это то же самое? — Нет. 中国 (Zhōngguó) — «Срединное государство», современное самоназвание; 天下 — более древнее и широкое «всё под небом».</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>FAQ 4</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>«Поднебесная» — это официально? — Сейчас в русском это поэтичное, образное имя Китая, а не официальное название.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Подпись-финал</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Тёплое пожелание от Юлии + приглашение задавать вопросы в комментариях (без рекламы).</t>
         </is>

--- a/content/tz-dzen-pochemu-kitaj-podnebesnaya.xlsx
+++ b/content/tz-dzen-pochemu-kitaj-podnebesnaya.xlsx
@@ -14,7 +14,7 @@
     <sheet name="5. Матрица триплетов" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="6. Факты" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="7. Готовые блоки" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8. Картинки и правила" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="8. Картинки и проверка фактов" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>подпись автора (нейтральная), хэштеги, источники</t>
+          <t>подпись автора (нейтральная), хэштеги — БЕЗ блока FAQ и БЕЗ источников</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Паспорт + FAQ</t>
+          <t>Паспорт</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1419,46 +1419,58 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Источник 1</t>
+          <t>Проверка фактов</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Wikipedia — Tianxia (天下, All Under Heaven)</t>
+          <t>Источники ниже — только для проверки достоверности; в статью блок «Источники» НЕ выносим.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Источник 2</t>
+          <t>Источник 1</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Wikipedia — Son of Heaven (天子) / Mandate of Heaven (天命)</t>
+          <t>Wikipedia — Tianxia (天下, All Under Heaven)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Источник 3</t>
+          <t>Источник 2</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Wikipedia — Names of China / 中国 (Zhongguo)</t>
+          <t>Wikipedia — Son of Heaven (天子) / Mandate of Heaven (天命)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>Источник 3</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Wikipedia — Names of China / 中国 (Zhongguo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
           <t>Источник 4</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Практика преподавания Kitai School</t>
         </is>

--- a/content/tz-dzen-pochemu-kitaj-podnebesnaya.xlsx
+++ b/content/tz-dzen-pochemu-kitaj-podnebesnaya.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -946,36 +946,48 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>H2 Из практики (в СЕРЕДИНЕ)</t>
+          <t>H2 Что это даёт тому, кто учит язык</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>личное наблюдение Юлии — как это всплывает в языке/на уроках</t>
+          <t>вывод от автора — как понимание слова помогает в изучении</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>H2 Что это даёт изучающему</t>
+          <t>Личные наблюдения</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>вывод: понимание слова помогает чувствовать язык и культуру</t>
+          <t>вплетаем по тексту, где уместно — БЕЗ отдельного блока «Из практики»</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>Выводы</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>доводим мысль прямо в тексте — БЕЗ отдельного блока «Вывод»</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>Финал</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>подпись автора (нейтральная), хэштеги — БЕЗ блока FAQ и БЕЗ источников</t>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>подпись автора (нейтральная), хэштеги — БЕЗ блоков FAQ и «Источники»</t>
         </is>
       </c>
     </row>
